--- a/jira_export_2026-06-26.xlsx
+++ b/jira_export_2026-06-26.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>62,543 €</t>
+          <t>64,972 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>19,964 €</t>
+          <t>22,142 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>42,580 €</t>
+          <t>42,830 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>1331</v>
+        <v>2928.2</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>1331</v>
+        <v>2928.2</v>
       </c>
     </row>
     <row r="23">
@@ -4108,11 +4108,11 @@
       <c r="N47" s="13" t="n">
         <v>171.4</v>
       </c>
-      <c r="O47" s="17" t="n">
-        <v>85.7</v>
+      <c r="O47" s="13" t="n">
+        <v>171.4</v>
       </c>
       <c r="P47" s="13" t="n">
-        <v>68.56</v>
+        <v>137.12</v>
       </c>
     </row>
     <row r="48">
@@ -4389,10 +4389,10 @@
         <v>1000</v>
       </c>
       <c r="O51" s="17" t="n">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="P51" s="13" t="n">
-        <v>207.69</v>
+        <v>221.54</v>
       </c>
     </row>
     <row r="52">
@@ -6093,10 +6093,10 @@
         <v>500</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>1700</v>
+        <v>1950</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="76">
@@ -9028,11 +9028,11 @@
       <c r="N116" s="16" t="n">
         <v>1250</v>
       </c>
-      <c r="O116" s="17" t="n">
-        <v>1201.12</v>
+      <c r="O116" s="16" t="n">
+        <v>1651.54</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>129.85</v>
+        <v>178.54</v>
       </c>
     </row>
     <row r="117">
@@ -11631,7 +11631,7 @@
         <v>18</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
@@ -14117,10 +14117,10 @@
         <v>66535.84</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>62543.36799999999</v>
+        <v>64971.68799999999</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>136.78</v>
+        <v>142.02</v>
       </c>
     </row>
   </sheetData>
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>121.25</v>
+        <v>121.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15537,7 +15537,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>136.25</v>
+        <v>136.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -15644,16 +15644,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>392296</v>
+        <v>389868</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>194728</v>
+        <v>192385</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>197569</v>
+        <v>197483</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>160793</v>
+        <v>160707</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>18605</v>
@@ -15669,16 +15669,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>191771</v>
+        <v>189592</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>85022</v>
+        <v>82929</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>106749</v>
+        <v>106663</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>97830</v>
+        <v>97744</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>4070</v>
@@ -15694,10 +15694,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>200526</v>
+        <v>200276</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>109706</v>
+        <v>109456</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>90820</v>

--- a/jira_export_2026-06-26.xlsx
+++ b/jira_export_2026-06-26.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>64,972 €</t>
+          <t>65,652 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>42,830 €</t>
+          <t>43,510 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>708 h</t>
+          <t>713 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -8959,10 +8959,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="13" t="n">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>0</v>
+        <v>453.33</v>
       </c>
     </row>
     <row r="116">
@@ -14117,10 +14117,10 @@
         <v>66535.84</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>64971.68799999999</v>
+        <v>65651.68799999999</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>142.02</v>
+        <v>143.5</v>
       </c>
     </row>
   </sheetData>
@@ -15510,7 +15510,7 @@
         <v>318.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>91.5</v>
+        <v>96</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>592.2</v>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>389868</v>
+        <v>389188</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>192385</v>
+        <v>191705</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197483</v>
@@ -15694,10 +15694,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>200276</v>
+        <v>199596</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>109456</v>
+        <v>108776</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>90820</v>

--- a/jira_export_2026-06-26.xlsx
+++ b/jira_export_2026-06-26.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>65,652 €</t>
+          <t>65,802 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>22,142 €</t>
+          <t>22,292 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>713 h</t>
+          <t>715 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -13869,10 +13869,10 @@
         <v>500</v>
       </c>
       <c r="O191" s="17" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="P191" s="13" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="192">
@@ -14117,10 +14117,10 @@
         <v>66535.84</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>65651.68799999999</v>
+        <v>65801.68799999999</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>143.5</v>
+        <v>143.83</v>
       </c>
     </row>
   </sheetData>
@@ -15510,7 +15510,7 @@
         <v>318.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>592.2</v>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>389188</v>
+        <v>389038</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>191705</v>
+        <v>191555</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197483</v>
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189592</v>
+        <v>189442</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>82929</v>
+        <v>82779</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106663</v>

--- a/jira_export_2026-06-26.xlsx
+++ b/jira_export_2026-06-26.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>65,802 €</t>
+          <t>66,289 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>22,292 €</t>
+          <t>22,779 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>715 h</t>
+          <t>723 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P196"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>2928.2</v>
+        <v>2994.75</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>2928.2</v>
+        <v>1996.5</v>
       </c>
     </row>
     <row r="23">
@@ -5933,7 +5933,7 @@
         <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         <v>910</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>1456</v>
+        <v>1501.5</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>187.87</v>
+        <v>171.6</v>
       </c>
     </row>
     <row r="74">
@@ -6293,7 +6293,7 @@
         <v>3</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>5</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
@@ -9173,10 +9173,10 @@
         <v>1762.5</v>
       </c>
       <c r="O118" s="17" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="119">
@@ -11025,7 +11025,7 @@
         <v>14</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>250</v>
       </c>
       <c r="P145" s="13" t="n">
-        <v>125</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="146">
@@ -12671,7 +12671,7 @@
         <v>33</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
@@ -13938,18 +13938,18 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1197</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr"/>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr"/>
@@ -13966,14 +13966,14 @@
       <c r="H193" s="12" t="inlineStr"/>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J193" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K193" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L193" s="12" t="inlineStr"/>
       <c r="M193" s="12" t="inlineStr"/>
@@ -13990,18 +13990,18 @@
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C194" s="15" t="inlineStr"/>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E194" s="15" t="inlineStr"/>
@@ -14018,14 +14018,14 @@
       <c r="H194" s="15" t="inlineStr"/>
       <c r="I194" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J194" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K194" s="15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L194" s="15" t="inlineStr"/>
       <c r="M194" s="15" t="inlineStr"/>
@@ -14042,16 +14042,20 @@
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1147</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>Commune de COUTANCES</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr"/>
-      <c r="D195" s="12" t="inlineStr"/>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
       <c r="E195" s="12" t="inlineStr"/>
       <c r="F195" s="12" t="inlineStr">
         <is>
@@ -14060,7 +14064,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr"/>
@@ -14073,54 +14077,102 @@
         <v>4</v>
       </c>
       <c r="K195" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="12" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="L195" s="12" t="inlineStr"/>
+      <c r="M195" s="12" t="inlineStr"/>
+      <c r="N195" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1145</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BOLBEC</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr"/>
+      <c r="D196" s="15" t="inlineStr"/>
+      <c r="E196" s="15" t="inlineStr"/>
+      <c r="F196" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G196" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H196" s="15" t="inlineStr"/>
+      <c r="I196" s="15" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="J196" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K196" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-31452</t>
         </is>
       </c>
-      <c r="M195" s="12" t="inlineStr">
+      <c r="M196" s="15" t="inlineStr">
         <is>
           <t>00156409</t>
         </is>
       </c>
-      <c r="N195" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O195" s="13" t="n">
+      <c r="N196" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="P195" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="inlineStr">
+      <c r="P196" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B196" s="18" t="inlineStr"/>
-      <c r="C196" s="18" t="inlineStr"/>
-      <c r="D196" s="18" t="inlineStr"/>
-      <c r="E196" s="18" t="inlineStr"/>
-      <c r="F196" s="18" t="inlineStr"/>
-      <c r="G196" s="18" t="inlineStr"/>
-      <c r="H196" s="18" t="inlineStr"/>
-      <c r="I196" s="18" t="inlineStr"/>
-      <c r="J196" s="18" t="inlineStr"/>
-      <c r="K196" s="18" t="inlineStr"/>
-      <c r="L196" s="18" t="inlineStr"/>
-      <c r="M196" s="18" t="inlineStr"/>
-      <c r="N196" s="19" t="n">
+      <c r="B197" s="18" t="inlineStr"/>
+      <c r="C197" s="18" t="inlineStr"/>
+      <c r="D197" s="18" t="inlineStr"/>
+      <c r="E197" s="18" t="inlineStr"/>
+      <c r="F197" s="18" t="inlineStr"/>
+      <c r="G197" s="18" t="inlineStr"/>
+      <c r="H197" s="18" t="inlineStr"/>
+      <c r="I197" s="18" t="inlineStr"/>
+      <c r="J197" s="18" t="inlineStr"/>
+      <c r="K197" s="18" t="inlineStr"/>
+      <c r="L197" s="18" t="inlineStr"/>
+      <c r="M197" s="18" t="inlineStr"/>
+      <c r="N197" s="19" t="n">
         <v>66535.84</v>
       </c>
-      <c r="O196" s="19" t="n">
-        <v>65801.68799999999</v>
-      </c>
-      <c r="P196" s="19" t="n">
-        <v>143.83</v>
+      <c r="O197" s="19" t="n">
+        <v>66288.738</v>
+      </c>
+      <c r="P197" s="19" t="n">
+        <v>142.79</v>
       </c>
     </row>
   </sheetData>
@@ -14317,6 +14369,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId192"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15498,16 +15551,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>248.25</v>
+        <v>253</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>57.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>12.25</v>
+        <v>14.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>318.25</v>
+        <v>325</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>98</v>
@@ -15517,7 +15570,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15612,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>139.5</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -15644,10 +15697,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>389038</v>
+        <v>388551</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>191555</v>
+        <v>191068</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197483</v>
@@ -15669,10 +15722,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189442</v>
+        <v>188955</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>82779</v>
+        <v>82292</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106663</v>

--- a/jira_export_2026-06-26.xlsx
+++ b/jira_export_2026-06-26.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>66,289 €</t>
+          <t>67,074 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>43,510 €</t>
+          <t>44,295 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>723 h</t>
+          <t>725 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -898,21 +898,21 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -928,7 +928,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
@@ -6444,11 +6444,11 @@
       <c r="N80" s="16" t="n">
         <v>285</v>
       </c>
-      <c r="O80" s="17" t="n">
-        <v>0</v>
+      <c r="O80" s="16" t="n">
+        <v>285</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
     </row>
     <row r="81">
@@ -14169,10 +14169,10 @@
         <v>66535.84</v>
       </c>
       <c r="O197" s="19" t="n">
-        <v>66288.738</v>
+        <v>67073.738</v>
       </c>
       <c r="P197" s="19" t="n">
-        <v>142.79</v>
+        <v>144.48</v>
       </c>
     </row>
   </sheetData>
@@ -15563,7 +15563,7 @@
         <v>325</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>592.2</v>
@@ -15697,10 +15697,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>388551</v>
+        <v>387766</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>191068</v>
+        <v>190283</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197483</v>
@@ -15747,10 +15747,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>199596</v>
+        <v>198811</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>108776</v>
+        <v>107991</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>90820</v>
@@ -15776,7 +15776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15800,7 +15800,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 33 commande(s)</t>
+          <t>Épics créées ce mois — 34 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15855,22 +15855,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -15883,14 +15883,18 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr"/>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>32077</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="6">
@@ -16166,12 +16170,12 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -16181,7 +16185,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -16201,11 +16205,11 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>3500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="13">
@@ -16301,22 +16305,22 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -16336,32 +16340,32 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>1700</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -16371,7 +16375,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -16381,32 +16385,32 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>4250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -16416,7 +16420,7 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -16426,32 +16430,32 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -16461,7 +16465,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -16471,22 +16475,22 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>0</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -16496,7 +16500,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -16506,42 +16510,38 @@
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr"/>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>0</v>
+        <v>32077</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -16561,32 +16561,32 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>3370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -16606,32 +16606,32 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -16651,32 +16651,32 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>1775</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -16696,32 +16696,32 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -16741,32 +16741,32 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>500</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-34187</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -16779,35 +16779,39 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00171144</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>2625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -16827,32 +16831,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1095.5</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -16872,32 +16876,32 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>1890</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -16917,32 +16921,32 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>6655</v>
+        <v>755</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -16962,32 +16966,32 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>2300</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -17007,32 +17011,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>755</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -17052,32 +17056,32 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>1000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -17097,32 +17101,32 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="I32" s="27" t="n">
-        <v>1350</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -17135,39 +17139,35 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G33" s="15" t="inlineStr"/>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>1840</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -17187,32 +17187,32 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="I34" s="27" t="n">
-        <v>2200</v>
+        <v>895</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34187</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -17232,11 +17232,11 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>00171144</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="36">
@@ -17287,22 +17287,22 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -17322,38 +17322,62 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>895</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>33 commande(s)</t>
-        </is>
-      </c>
-      <c r="I38" s="25" t="n">
-        <v>109496</v>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34235</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34229</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>DIJON METROPOLE</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>00171333</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B39" s="18" t="n"/>
@@ -17364,17 +17388,17 @@
       <c r="G39" s="18" t="n"/>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>13 commande(s)</t>
+          <t>34 commande(s)</t>
         </is>
       </c>
       <c r="I39" s="25" t="n">
-        <v>35034</v>
+        <v>109496</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B40" s="18" t="n"/>
@@ -17385,10 +17409,31 @@
       <c r="G40" s="18" t="n"/>
       <c r="H40" s="18" t="inlineStr">
         <is>
+          <t>14 commande(s)</t>
+        </is>
+      </c>
+      <c r="I40" s="25" t="n">
+        <v>35034</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
           <t>20 commande(s)</t>
         </is>
       </c>
-      <c r="I40" s="25" t="n">
+      <c r="I41" s="25" t="n">
         <v>74462</v>
       </c>
     </row>
@@ -17403,7 +17448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -17424,7 +17469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20 clôture(s) : 16 projet(s), 4 rework</t>
+          <t>24 clôture(s) : 19 projet(s), 5 rework</t>
         </is>
       </c>
     </row>
@@ -17734,17 +17779,17 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32357</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CESTAS] - Accomp 1/2j</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CESTAS</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -17764,22 +17809,22 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-16171</t>
+          <t>PDMDEP-32357</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>[RODEZ] Littéralis expert</t>
+          <t>[COMMUNE DE CESTAS] - Accomp 1/2j</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>RODEZ</t>
+          <t>COMMUNE DE CESTAS</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -17788,28 +17833,28 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-17291</t>
+          <t>PDMDEP-33964</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>[EVREUX] Littéralis Expert</t>
+          <t>[COMMUNE DE GUIDEL] - Réparation PAX A920</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[EVREUX] </t>
+          <t>COMMUNE DE GUIDEL</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -17818,28 +17863,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-24410</t>
+          <t>PDMDEP-33976</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)] - Modé</t>
+          <t>[COMMUNE DE SAINT PRIEST] - Instal APK Placier x2</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)</t>
+          <t>COMMUNE DE SAINT PRIEST</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -17848,23 +17893,23 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-16171</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffr</t>
+          <t>[RODEZ] Littéralis expert</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>RODEZ</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -17878,23 +17923,23 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32009</t>
+          <t>PDMDEP-17291</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
+          <t>[EVREUX] Littéralis Expert</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
+          <t xml:space="preserve">[EVREUX] </t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
@@ -17908,186 +17953,306 @@
         </is>
       </c>
       <c r="F19" s="15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-24410</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)] - Modé</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31285</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffr</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LUNEL</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32009</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-33471</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>COMMUNE D AUCH</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F23" s="15" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-17131</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>[PAU] Migration GEODP</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>PAU</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-21265</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>SANARY SUR MER</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-23410</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-17131</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>[PAU] Migration GEODP</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>PAU</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>PDMDEP-21265</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>SANARY SUR MER</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>PDMDEP-23419</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN - GEODP2 migratio</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>PDMDEP-23410</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-24216</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F28" s="28" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29" t="n">
-        <v>4</v>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-06-26.xlsx
+++ b/jira_export_2026-06-26.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>725 h</t>
+          <t>728 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -10057,7 +10057,7 @@
         <v>9</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>4.12</v>
+        <v>4.62</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>9</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>4.12</v>
+        <v>4.62</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L186" s="15" t="inlineStr">
         <is>
@@ -14148,31 +14148,187 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="18" t="inlineStr">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B197" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr"/>
+      <c r="D197" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E197" s="12" t="inlineStr"/>
+      <c r="F197" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G197" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H197" s="12" t="inlineStr"/>
+      <c r="I197" s="12" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J197" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K197" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L197" s="12" t="inlineStr"/>
+      <c r="M197" s="12" t="inlineStr"/>
+      <c r="N197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="14" t="inlineStr">
+        <is>
+          <t>PSC-817</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>PLATEAU D'HAUTEVILLE</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr"/>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>PLATEAU D'HAUTEVILLE</t>
+        </is>
+      </c>
+      <c r="E198" s="15" t="inlineStr"/>
+      <c r="F198" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G198" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H198" s="15" t="inlineStr"/>
+      <c r="I198" s="15" t="inlineStr">
+        <is>
+          <t>15/05/2025</t>
+        </is>
+      </c>
+      <c r="J198" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K198" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L198" s="15" t="inlineStr"/>
+      <c r="M198" s="15" t="inlineStr"/>
+      <c r="N198" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr"/>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E199" s="12" t="inlineStr"/>
+      <c r="F199" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G199" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H199" s="12" t="inlineStr"/>
+      <c r="I199" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J199" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K199" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L199" s="12" t="inlineStr"/>
+      <c r="M199" s="12" t="inlineStr"/>
+      <c r="N199" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B197" s="18" t="inlineStr"/>
-      <c r="C197" s="18" t="inlineStr"/>
-      <c r="D197" s="18" t="inlineStr"/>
-      <c r="E197" s="18" t="inlineStr"/>
-      <c r="F197" s="18" t="inlineStr"/>
-      <c r="G197" s="18" t="inlineStr"/>
-      <c r="H197" s="18" t="inlineStr"/>
-      <c r="I197" s="18" t="inlineStr"/>
-      <c r="J197" s="18" t="inlineStr"/>
-      <c r="K197" s="18" t="inlineStr"/>
-      <c r="L197" s="18" t="inlineStr"/>
-      <c r="M197" s="18" t="inlineStr"/>
-      <c r="N197" s="19" t="n">
+      <c r="B200" s="18" t="inlineStr"/>
+      <c r="C200" s="18" t="inlineStr"/>
+      <c r="D200" s="18" t="inlineStr"/>
+      <c r="E200" s="18" t="inlineStr"/>
+      <c r="F200" s="18" t="inlineStr"/>
+      <c r="G200" s="18" t="inlineStr"/>
+      <c r="H200" s="18" t="inlineStr"/>
+      <c r="I200" s="18" t="inlineStr"/>
+      <c r="J200" s="18" t="inlineStr"/>
+      <c r="K200" s="18" t="inlineStr"/>
+      <c r="L200" s="18" t="inlineStr"/>
+      <c r="M200" s="18" t="inlineStr"/>
+      <c r="N200" s="19" t="n">
         <v>66535.84</v>
       </c>
-      <c r="O197" s="19" t="n">
+      <c r="O200" s="19" t="n">
         <v>67073.738</v>
       </c>
-      <c r="P197" s="19" t="n">
-        <v>144.48</v>
+      <c r="P200" s="19" t="n">
+        <v>143.63</v>
       </c>
     </row>
   </sheetData>
@@ -14370,6 +14526,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId195"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15551,16 +15710,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>253</v>
+        <v>254.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>57.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>14.25</v>
+        <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>325</v>
+        <v>327.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>100</v>
@@ -15570,7 +15729,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
